--- a/FPPN_Demandes_au_FPPN_20261023.xlsx
+++ b/FPPN_Demandes_au_FPPN_20261023.xlsx
@@ -870,7 +870,7 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>La garantie santé des policiers retraités est-elle accordée à vie ou pour une durée limitée ? Quelle est leur cotisation ?</t>
+          <t>La garantie santé des policiers retraités est-elle accordée à vie ou pour une durée limitée ? (Le barème de cotisation de la CGRAE a été reçu le 23/10/2026.)</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Avenants à la convention IPS-CGRAE, son annexe 2 (bulletin de souscription), barème de la cotisation des retraités et liste des retraités souscripteurs non précomptés.</t>
+          <t>Avenants à la convention IPS-CGRAE, son annexe 2 (bulletin de souscription) et liste des retraités souscripteurs non précomptés (le barème de la cotisation des retraités est reçu le 23/10/2026).</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>Liste des prestataires de santé conventionnés et conventions signées (tarifs, taux de prise en charge, plafonds).</t>
-        </is>
-      </c>
-      <c r="E28" s="5" t="inlineStr">
-        <is>
-          <t>Non reçu</t>
+          <t>Conventions signées avec chaque prestataire de santé conventionné (tarifs, taux de prise en charge, plafonds) et date d'application du barème tarifaire du FPPN (reçu le 23/10/2026, non daté, mention « tarifications proposées »).</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>Partiellement reçu</t>
         </is>
       </c>
       <c r="F28" s="6" t="inlineStr">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>Durée de la garantie santé des retraités (à vie ou limitée), cotisation et ayants droit couverts, et décision qui la fonde.</t>
+          <t>Durée de la garantie santé des retraités (à vie ou limitée), ayants droit couverts et décision qui la fonde (le barème de la cotisation est reçu le 23/10/2026).</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
@@ -3876,12 +3876,12 @@
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>Procédure écrite du circuit des fichiers aller et retour de chaque produit (maladie, décès, EFC, PEP, Grenier, MEDOC, flotte, retraités) : qui produit, qui transmet, qui reçoit, qui rapproche.</t>
-        </is>
-      </c>
-      <c r="E86" s="5" t="inlineStr">
-        <is>
-          <t>Non reçu</t>
+          <t>Procédure écrite pour le Grenier (9X4) et MEDOC (8Z7), et description du rapprochement des fichiers aller et retour (les logigrammes de l'EFC, du PEP, de la flotte, de la CGRAE, de la maladie et du décès sont reçus le 23/10/2026).</t>
+        </is>
+      </c>
+      <c r="E86" s="6" t="inlineStr">
+        <is>
+          <t>Partiellement reçu</t>
         </is>
       </c>
       <c r="F86" s="7" t="inlineStr">
